--- a/output/(山本)整合性_無矛盾性_再構成.xlsx
+++ b/output/(山本)整合性_無矛盾性_再構成.xlsx
@@ -461,14 +461,14 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>上位ドキュメントの要求（性能目標、制約条件等）を、下位ドキュメントが論理的な不整合なく具現化している。特に、処理タイミング、計算式、データ精度といった定量的側面において、上下関係にある定義が完全に一致している。</t>
+          <t>関連する複数の成果物（要件定義書と基本設計書など）を突合した際、データの更新頻度、処理方式、性能要件などの仕様設定値に論理的な衝突がなく、同一のシステム要件として矛盾なく実装可能な状態であることを確認している。</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
           <t>★新規追加
-【非適合例】システム要件定義書にて「データのリアルタイム更新」を規定しながら、詳細設計書では「1時間間隔のバッチ処理による更新」を定義している（動作タイミングの齟齬）。
-→【適合例】システム要件定義書で掲げた「データのリアルタイム更新」に対し、詳細設計書において「MQ通信を利用した即時データ同期処理」を具体的に定義している。</t>
+【非適合例】（システム要件定義書）データはリアルタイムで連携・更新される。（基本設計書）当該データは1時間ごとのバッチ処理で一括更新される。（非適合の理由：要件定義と基本設計間でデータの更新頻度に関する仕様設定が衝突し、実装不可となっているため。）
+→【適合例】（システム要件定義書）データはリアルタイムで連携・更新される。（基本設計書）当該データはメッセージキューイングを用いて非同期かつリアルタイムに更新処理を実行する。</t>
         </is>
       </c>
     </row>
@@ -480,14 +480,14 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>同一ドキュメント内において、特定の機能やデータに対する状態遷移、例外処理、排他制御などの条件定義が、章節をまたいで論理的に相反していない。一つの事象に対し、一貫した処理ロジックが成立している。</t>
+          <t>同一の仕様書内において特定の機能に対する業務ルール、状態遷移、制約条件などを複数定義する際、デシジョンテーブルや状態遷移表を用いて互いの前提事項に論理的な破綻がないことを検証し、すべての条件が両立可能であることを明記している。</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
           <t>★新規追加
-【非適合例】「入力データは逐次自動保存する」という記述と、「保存ボタンの押下によって確定する」という記述が混在している（保存トリガーの不一致）。
-→【適合例】「入力データは逐次自動保存する」とした上で、別の記述箇所にて「保存完了時にはステータスバーに通知を表示する」と、一貫した動作として定義している。</t>
+【非適合例】（システム要件A）入力データは自動的に保存される。（システム要件B）データの保存処理を実行するには、ユーザーによる「保存」ボタンの明示的な押下を必須とする。（非適合の理由：同一機能に対するデータの保存トリガー条件が矛盾して定義されており、条件の両立が不可能であるため。）
+→【適合例】（システム要件A）入力データはバックグラウンド処理により5分間隔で自動的に一時保存される。（システム要件B）一時保存されたデータは、ユーザーが「確定」ボタンを押下した時点で本登録状態に移行する。</t>
         </is>
       </c>
     </row>
@@ -499,14 +499,14 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>上位文書で定義された全ての要求事項が、下位文書の設計項目として過不足なく割り当てられている。各要求の実現手段が具体化されており、上位の目的と下位の手段が1対1または1対Nの関係で明確に関連付けられている。</t>
+          <t>上位レベルの要求事項とそれを実現するための下位レベルのシステム機能設計が、要件IDやトレーサビリティマトリクスを用いて対応付けられており、要件にない機能の追加や必須要求の欠落がないことを客観的に追跡可能な状態で明記している。</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
           <t>★新規追加
-【非適合例】上位の要件定義書で「多要素認証の導入」を求めているが、下位の基本設計書には「IDとパスワードによる認証」のみが記載され、他の認証要素が欠落している（網羅性の欠如）。
-→【適合例】上位の要件定義書における「多要素認証の導入」に対し、下位の基本設計書で「知識認証（パスワード）と所有物認証（FIDO2準拠デバイス）の併用」を定義している。</t>
+【非適合例】（上位要求）顧客は自身の過去の注文履歴を一覧表示できる。（下位設計）おすすめ商品の一覧を取得するAPIを実装する。（非適合の理由：上位の注文履歴表示要求に対して下位設計で全く異なる機能の仕様が記載されており、本来の要求に対する設計が欠落しているため。）
+→【適合例】（上位要求：REQ-01）顧客は自身の過去の注文履歴を一覧表示できる。（下位設計：DSG-01/REQ-01対応）顧客IDをキーとして注文履歴テーブルを検索し、購入日時の降順で一覧を取得するAPIを実装する。</t>
         </is>
       </c>
     </row>
@@ -518,13 +518,14 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>システム全体に共通する用語、アーキテクチャ、外部インターフェース定義等が、各文書間で共通の認識に基づき記述されている。重複定義を避け、共通仕様は原本（マスター文書）を特定し、他からは参照形式で記述することで整合性を担保している。</t>
+          <t>システムアーキテクチャや共通仕様などの横断的な情報は、各機能の仕様書内に分散させて重複記述せず、一元管理された共通仕様書やアーキテクチャ定義書に集約した上で、個別の仕様書からはドキュメント名と章節番号による参照関係を用いて論理的な整合性を維持している。</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>【非適合例】同一のシステム構成図が複数の機能仕様書に転記されており、一部の文書にのみ古い構成情報が残存している（多重定義による情報の不整合）。
-→【適合例】システム構成を「システムアーキテクチャ仕様書」に集約して記述し、各機能仕様書からは当該仕様書を最新の参照先として指定している。</t>
+          <t>★新規追加
+【非適合例】（機能仕様書A）本システムはクラウド環境上に構築され、データベースにはマネージドサービスを使用する。（機能仕様書B）本システムはクラウド環境上に構築され、データベースにはマネージドサービスを使用する。（非適合の理由：システム全体のアーキテクチャ方針が個別の機能仕様書内に分散して重複記述されており、文書間の関係が整合していないため。）
+→【適合例】（機能仕様書A）本システムのアーキテクチャおよびインフラ構成方針については、「システムアーキテクチャ仕様書第2章」を参照すること。</t>
         </is>
       </c>
     </row>
